--- a/output/stock_quant_scores/BATS.L_info.xlsx
+++ b/output/stock_quant_scores/BATS.L_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FL2"/>
+  <dimension ref="A1:FJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,375 +891,365 @@
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
       <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1385,34 +1375,34 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>3897</v>
+        <v>3934</v>
       </c>
       <c r="AD2" t="n">
-        <v>3935</v>
+        <v>3920</v>
       </c>
       <c r="AE2" t="n">
-        <v>3853</v>
+        <v>3896</v>
       </c>
       <c r="AF2" t="n">
-        <v>3953</v>
+        <v>3950</v>
       </c>
       <c r="AG2" t="n">
-        <v>3897</v>
+        <v>3934</v>
       </c>
       <c r="AH2" t="n">
-        <v>3935</v>
+        <v>3920</v>
       </c>
       <c r="AI2" t="n">
-        <v>3851</v>
+        <v>3896</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3953</v>
+        <v>3950</v>
       </c>
       <c r="AK2" t="n">
         <v>2.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="AM2" t="n">
         <v>1759363200</v>
@@ -1427,31 +1417,31 @@
         <v>0.159</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28.021584</v>
+        <v>28.345325</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.10475781</v>
+        <v>0.1059681</v>
       </c>
       <c r="AS2" t="n">
-        <v>3558212</v>
+        <v>2602064</v>
       </c>
       <c r="AT2" t="n">
-        <v>3501813</v>
+        <v>2602064</v>
       </c>
       <c r="AU2" t="n">
-        <v>4427669</v>
+        <v>4342631</v>
       </c>
       <c r="AV2" t="n">
-        <v>4298191</v>
+        <v>4515785</v>
       </c>
       <c r="AW2" t="n">
-        <v>4298191</v>
+        <v>4515785</v>
       </c>
       <c r="AX2" t="n">
-        <v>3887</v>
+        <v>3939</v>
       </c>
       <c r="AY2" t="n">
-        <v>3889</v>
+        <v>3940</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1460,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>84962631680</v>
+        <v>85929254912</v>
       </c>
       <c r="BC2" t="n">
         <v>2621.79</v>
@@ -1475,19 +1465,19 @@
         <v>116.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.3193715</v>
+        <v>3.357136</v>
       </c>
       <c r="BH2" t="n">
-        <v>4107.8</v>
+        <v>4113.22</v>
       </c>
       <c r="BI2" t="n">
-        <v>3434.93</v>
+        <v>3449.835</v>
       </c>
       <c r="BJ2" t="n">
         <v>2.402</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0006163716</v>
+        <v>0.00061057444</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1498,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>116235182080</v>
+        <v>117178597376</v>
       </c>
       <c r="BO2" t="n">
         <v>0.12064</v>
       </c>
       <c r="BP2" t="n">
-        <v>1861740640</v>
+        <v>1823192060</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2181325596</v>
+        <v>2180945330</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.09034</v>
+        <v>0.09036</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.52437</v>
+        <v>0.52717</v>
       </c>
       <c r="BT2" t="n">
         <v>2200636410</v>
@@ -1522,7 +1512,7 @@
         <v>20.597</v>
       </c>
       <c r="BV2" t="n">
-        <v>189.10521</v>
+        <v>191.29</v>
       </c>
       <c r="BW2" t="n">
         <v>1735603200</v>
@@ -1546,16 +1536,16 @@
         <v>371.81</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.541</v>
+        <v>4.578</v>
       </c>
       <c r="CE2" t="n">
-        <v>9.476000000000001</v>
+        <v>9.553000000000001</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.3712175</v>
+        <v>0.4464023</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CH2" t="n">
         <v>0.6006</v>
@@ -1569,7 +1559,7 @@
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>3895</v>
+        <v>3940</v>
       </c>
       <c r="CL2" t="n">
         <v>5200</v>
@@ -1583,272 +1573,264 @@
       <c r="CO2" t="n">
         <v>4400</v>
       </c>
-      <c r="CP2" t="n">
-        <v>2.16667</v>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CQ2" t="n">
+        <v>12</v>
       </c>
       <c r="CR2" t="n">
-        <v>12</v>
+        <v>4893000192</v>
       </c>
       <c r="CS2" t="n">
-        <v>4893000192</v>
+        <v>2.23</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.23</v>
+        <v>12266000384</v>
       </c>
       <c r="CU2" t="n">
-        <v>12266000384</v>
+        <v>35325001728</v>
       </c>
       <c r="CV2" t="n">
-        <v>35325001728</v>
+        <v>0.53</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.53</v>
+        <v>0.867</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.867</v>
+        <v>25596000256</v>
       </c>
       <c r="CY2" t="n">
-        <v>25596000256</v>
+        <v>74.878</v>
       </c>
       <c r="CZ2" t="n">
-        <v>74.878</v>
+        <v>11.637</v>
       </c>
       <c r="DA2" t="n">
-        <v>11.637</v>
+        <v>0.0559</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0559</v>
+        <v>0.06271</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.06271</v>
+        <v>21208999936</v>
       </c>
       <c r="DD2" t="n">
-        <v>21208999936</v>
+        <v>9270750208</v>
       </c>
       <c r="DE2" t="n">
-        <v>9270750208</v>
+        <v>9269000192</v>
       </c>
       <c r="DF2" t="n">
-        <v>9269000192</v>
+        <v>0.016</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.016</v>
+        <v>-0.022</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.022</v>
+        <v>0.82861</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.82861</v>
+        <v>0.47922</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.47922</v>
-      </c>
-      <c r="DK2" t="n">
         <v>0.42042</v>
       </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>BATS.L</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>BATS.L</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DR2" t="b">
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>1753975800</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1753975800</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1753975800</v>
+          <t>LSE</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>finmb_326614</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>BST</t>
+        </is>
       </c>
       <c r="DW2" t="n">
-        <v>1753950600</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1753950600</v>
+        <v>3600000</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>gb_market</t>
+        </is>
       </c>
       <c r="DY2" t="b">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
+        <v>0.15251653</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>3940</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Dividend', 'message': 'BATS.L announced a cash dividend of 0.601 with an ex-date of Oct. 2, 2025', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1759359600000, 'amount': '0.601'}}]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1758902437</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>4342631</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1318.21</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.50279003</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>2621.79 - 4401.0</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>-461</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.10474892</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>44.640232</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1753975800</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1753975800</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1753975800</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1753950600</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1753950600</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
         <v>1.39</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="ES2" t="n">
         <v>371.81</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="ET2" t="n">
         <v>3.38995</v>
       </c>
-      <c r="EC2" t="n">
-        <v>1148.9845</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-212.7998</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.05180384</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>460.07007</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.1339387</v>
-      </c>
-      <c r="EH2" t="n">
+      <c r="EU2" t="n">
+        <v>1162.259</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-173.22021</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.042113043</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>490.16504</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.14208362</v>
+      </c>
+      <c r="EZ2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="FA2" t="n">
         <v>15</v>
       </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>2.2 - Buy</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>3851.0 - 3953.0</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
+      <c r="FB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>789120000000</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>3896.0 - 3950.0</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
         <is>
           <t>LSE</t>
         </is>
       </c>
-      <c r="EN2" t="n">
-        <v>4427669</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1273.21</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.48562622</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>2621.79 - 4401.0</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>-506</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.11497387</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>37.12175</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': 'BATS.L announced a cash dividend of 0.601 with an ex-date of Oct. 2, 2025', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1759359600000, 'amount': '0.601'}}]</t>
-        </is>
-      </c>
-      <c r="EV2" t="n">
-        <v>1758732404</v>
-      </c>
-      <c r="EW2" t="inlineStr">
+      <c r="FH2" t="inlineStr">
         <is>
           <t>BRITISH AMERICAN TOBACCO PLC OR</t>
         </is>
       </c>
-      <c r="EX2" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>POSTPOST</t>
-        </is>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>LSE</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>finmb_326614</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>Europe/London</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>BST</t>
-        </is>
-      </c>
-      <c r="FE2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>gb_market</t>
-        </is>
-      </c>
-      <c r="FG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>-0.051321533</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>3895</v>
-      </c>
-      <c r="FJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>789120000000</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>0.4043</v>
+      <c r="FJ2" t="n">
+        <v>0.4088</v>
       </c>
     </row>
   </sheetData>
